--- a/서버정보/20261002_리소스배포_개발.xlsx
+++ b/서버정보/20261002_리소스배포_개발.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2902AEE8-0F6F-4E39-A317-DAFB1771859B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CECFE18-4714-449A-B786-DE64142D3044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -2531,7 +2531,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2661,10 +2661,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -10457,6 +10454,7 @@
       <c r="AF61" s="8"/>
     </row>
     <row r="62" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A62" s="38"/>
       <c r="B62" s="8" t="s">
         <v>31</v>
       </c>
@@ -10545,6 +10543,7 @@
       <c r="AF62" s="8"/>
     </row>
     <row r="63" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A63" s="38"/>
       <c r="B63" s="8" t="s">
         <v>31</v>
       </c>
@@ -10633,6 +10632,7 @@
       <c r="AF63" s="8"/>
     </row>
     <row r="64" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A64" s="38"/>
       <c r="B64" s="8" t="s">
         <v>31</v>
       </c>
@@ -10720,7 +10720,8 @@
       <c r="AE64" s="8"/>
       <c r="AF64" s="8"/>
     </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A65" s="38"/>
       <c r="B65" s="8" t="s">
         <v>31</v>
       </c>
@@ -10808,7 +10809,8 @@
       <c r="AE65" s="8"/>
       <c r="AF65" s="8"/>
     </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A66" s="38"/>
       <c r="B66" s="8" t="s">
         <v>31</v>
       </c>
@@ -10816,7 +10818,7 @@
         <f t="array" ref="C66">UPPER(INDEX(_xlfn.TEXTSPLIT($D66, "-"), 3))</f>
         <v>GA</v>
       </c>
-      <c r="D66" s="43" t="s">
+      <c r="D66" s="8" t="s">
         <v>449</v>
       </c>
       <c r="E66" s="8" t="s">
@@ -10849,7 +10851,7 @@
       <c r="N66" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="O66" s="43" t="str">
+      <c r="O66" s="8" t="str">
         <f>SUBSTITUTE(F66,"hazr-","")&amp;"-osdisk"</f>
         <v>d-ga-oap01-osdisk</v>
       </c>
@@ -10859,10 +10861,10 @@
       <c r="Q66" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="R66" s="43"/>
+      <c r="R66" s="8"/>
       <c r="S66" s="8"/>
-      <c r="T66" s="43"/>
-      <c r="U66" s="43" t="str">
+      <c r="T66" s="8"/>
+      <c r="U66" s="8" t="str">
         <f>SUBSTITUTE(F66,"hazr-","")&amp;"-nic"</f>
         <v>d-ga-oap01-nic</v>
       </c>
@@ -10896,7 +10898,8 @@
       <c r="AE66" s="8"/>
       <c r="AF66" s="8"/>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A67" s="38"/>
       <c r="B67" s="8" t="s">
         <v>31</v>
       </c>
@@ -10904,7 +10907,7 @@
         <f t="array" ref="C67">UPPER(INDEX(_xlfn.TEXTSPLIT($D67, "-"), 3))</f>
         <v>BSU</v>
       </c>
-      <c r="D67" s="43" t="s">
+      <c r="D67" s="8" t="s">
         <v>452</v>
       </c>
       <c r="E67" s="8" t="s">
@@ -10937,7 +10940,7 @@
       <c r="N67" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="O67" s="43" t="str">
+      <c r="O67" s="8" t="str">
         <f>SUBSTITUTE(F67,"hazr-","")&amp;"-osdisk"</f>
         <v>d-bsu-cirsweb01-osdisk</v>
       </c>
@@ -10947,10 +10950,10 @@
       <c r="Q67" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="R67" s="43"/>
+      <c r="R67" s="8"/>
       <c r="S67" s="8"/>
-      <c r="T67" s="43"/>
-      <c r="U67" s="43" t="str">
+      <c r="T67" s="8"/>
+      <c r="U67" s="8" t="str">
         <f>SUBSTITUTE(F67,"hazr-","")&amp;"-nic"</f>
         <v>d-bsu-cirsweb01-nic</v>
       </c>
@@ -10984,7 +10987,8 @@
       <c r="AE67" s="8"/>
       <c r="AF67" s="8"/>
     </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A68" s="38"/>
       <c r="B68" s="8" t="s">
         <v>31</v>
       </c>
@@ -10992,7 +10996,7 @@
         <f t="array" ref="C68">UPPER(INDEX(_xlfn.TEXTSPLIT($D68, "-"), 3))</f>
         <v>BSU</v>
       </c>
-      <c r="D68" s="43" t="s">
+      <c r="D68" s="8" t="s">
         <v>452</v>
       </c>
       <c r="E68" s="8" t="s">
@@ -11025,7 +11029,7 @@
       <c r="N68" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="O68" s="43" t="str">
+      <c r="O68" s="8" t="str">
         <f>SUBSTITUTE(F68,"hazr-","")&amp;"-osdisk"</f>
         <v>d-bsu-cirsap01-osdisk</v>
       </c>
@@ -11035,10 +11039,10 @@
       <c r="Q68" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="R68" s="43"/>
+      <c r="R68" s="8"/>
       <c r="S68" s="8"/>
-      <c r="T68" s="43"/>
-      <c r="U68" s="43" t="str">
+      <c r="T68" s="8"/>
+      <c r="U68" s="8" t="str">
         <f>SUBSTITUTE(F68,"hazr-","")&amp;"-nic"</f>
         <v>d-bsu-cirsap01-nic</v>
       </c>
@@ -14733,6 +14737,7 @@
       <c r="R66" s="14"/>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A67" s="38"/>
       <c r="B67" s="15" t="s">
         <v>31</v>
       </c>
@@ -14787,6 +14792,7 @@
       <c r="R67" s="15"/>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A68" s="38"/>
       <c r="B68" s="14" t="s">
         <v>31</v>
       </c>
@@ -14841,6 +14847,7 @@
       <c r="R68" s="14"/>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A69" s="38"/>
       <c r="B69" s="15" t="s">
         <v>31</v>
       </c>
@@ -14895,6 +14902,7 @@
       <c r="R69" s="15"/>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A70" s="38"/>
       <c r="B70" s="14" t="s">
         <v>31</v>
       </c>
@@ -14949,6 +14957,7 @@
       <c r="R70" s="14"/>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A71" s="38"/>
       <c r="B71" s="15" t="s">
         <v>31</v>
       </c>
@@ -15003,6 +15012,7 @@
       <c r="R71" s="15"/>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A72" s="38"/>
       <c r="B72" s="14" t="s">
         <v>31</v>
       </c>
@@ -15057,6 +15067,7 @@
       <c r="R72" s="14"/>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A73" s="38"/>
       <c r="B73" s="15" t="s">
         <v>31</v>
       </c>
@@ -17068,7 +17079,7 @@
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="44"/>
+      <c r="A51" s="6"/>
       <c r="B51" s="33" t="s">
         <v>31</v>
       </c>
@@ -17100,7 +17111,7 @@
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="44"/>
+      <c r="A52" s="6"/>
       <c r="B52" s="32" t="s">
         <v>31</v>
       </c>
@@ -17514,7 +17525,7 @@
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" s="44"/>
+      <c r="A65" s="9"/>
       <c r="B65" s="30" t="s">
         <v>31</v>
       </c>
@@ -17546,7 +17557,7 @@
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A66" s="44"/>
+      <c r="A66" s="9"/>
       <c r="B66" s="32" t="s">
         <v>31</v>
       </c>
@@ -17578,7 +17589,7 @@
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A67" s="44"/>
+      <c r="A67" s="9"/>
       <c r="B67" s="30" t="s">
         <v>31</v>
       </c>
@@ -17610,7 +17621,7 @@
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A68" s="44"/>
+      <c r="A68" s="9"/>
       <c r="B68" s="32" t="s">
         <v>31</v>
       </c>
@@ -18300,7 +18311,7 @@
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A86" s="6"/>
+      <c r="A86" s="9"/>
       <c r="B86" s="32" t="s">
         <v>31</v>
       </c>
@@ -18328,7 +18339,7 @@
         <v>445</v>
       </c>
       <c r="J86" s="32" t="s">
-        <v>52</v>
+        <v>448</v>
       </c>
       <c r="K86" s="32" t="str">
         <f t="shared" si="5"/>
@@ -18339,7 +18350,7 @@
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A87" s="6"/>
+      <c r="A87" s="9"/>
       <c r="B87" s="14" t="s">
         <v>31</v>
       </c>
@@ -18367,7 +18378,7 @@
         <v>446</v>
       </c>
       <c r="J87" s="14" t="s">
-        <v>52</v>
+        <v>448</v>
       </c>
       <c r="K87" s="14" t="str">
         <f t="shared" si="5"/>
@@ -18378,7 +18389,7 @@
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A88" s="6"/>
+      <c r="A88" s="9"/>
       <c r="B88" s="32" t="s">
         <v>31</v>
       </c>
@@ -18406,7 +18417,7 @@
         <v>447</v>
       </c>
       <c r="J88" s="32" t="s">
-        <v>52</v>
+        <v>448</v>
       </c>
       <c r="K88" s="32" t="str">
         <f t="shared" si="5"/>
@@ -18417,7 +18428,7 @@
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A89" s="6"/>
+      <c r="A89" s="9"/>
       <c r="B89" s="14" t="s">
         <v>31</v>
       </c>
@@ -18445,7 +18456,7 @@
         <v>450</v>
       </c>
       <c r="J89" s="14" t="s">
-        <v>52</v>
+        <v>449</v>
       </c>
       <c r="K89" s="14" t="str">
         <f t="shared" si="5"/>
@@ -18456,6 +18467,7 @@
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A90" s="43"/>
       <c r="B90" s="32" t="s">
         <v>31</v>
       </c>
@@ -18483,7 +18495,7 @@
         <v>451</v>
       </c>
       <c r="J90" s="32" t="s">
-        <v>52</v>
+        <v>449</v>
       </c>
       <c r="K90" s="32" t="str">
         <f t="shared" si="5"/>
@@ -18494,6 +18506,7 @@
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A91" s="43"/>
       <c r="B91" s="14" t="s">
         <v>31</v>
       </c>
@@ -18521,7 +18534,7 @@
         <v>453</v>
       </c>
       <c r="J91" s="14" t="s">
-        <v>52</v>
+        <v>452</v>
       </c>
       <c r="K91" s="14" t="str">
         <f t="shared" si="5"/>
@@ -18532,6 +18545,7 @@
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A92" s="43"/>
       <c r="B92" s="32" t="s">
         <v>31</v>
       </c>
@@ -18559,7 +18573,7 @@
         <v>454</v>
       </c>
       <c r="J92" s="32" t="s">
-        <v>52</v>
+        <v>452</v>
       </c>
       <c r="K92" s="32" t="str">
         <f t="shared" si="5"/>
@@ -18590,6 +18604,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -18733,12 +18753,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
@@ -18748,6 +18762,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18763,20 +18793,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>